--- a/data/trans_camb/IP15-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP15-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 18,17</t>
+          <t>-7,59; 17,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 19,16</t>
+          <t>-7,53; 18,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,88; 38,43</t>
+          <t>4,11; 36,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 20,53</t>
+          <t>-3,67; 20,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 23,31</t>
+          <t>-2,68; 21,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 20,45</t>
+          <t>-3,21; 20,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 16,7</t>
+          <t>-2,07; 16,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 16,44</t>
+          <t>-0,92; 17,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 24,37</t>
+          <t>3,93; 24,47</t>
         </is>
       </c>
     </row>
@@ -783,54 +783,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-31,24; 108,33</t>
+          <t>-28,47; 113,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-29,21; 121,87</t>
+          <t>-28,0; 117,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,97; 231,97</t>
+          <t>9,89; 221,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,55; 141,37</t>
+          <t>-14,21; 137,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,39; 174,07</t>
+          <t>-10,41; 150,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,28; 152,88</t>
+          <t>-14,73; 144,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 98,73</t>
+          <t>-9,67; 98,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 99,41</t>
+          <t>-3,95; 106,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,96; 145,95</t>
+          <t>12,34; 147,23</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 13,53</t>
+          <t>-2,63; 15,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 18,86</t>
+          <t>-0,19; 17,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,79; 61,54</t>
+          <t>18,37; 59,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 12,67</t>
+          <t>-4,74; 13,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 8,69</t>
+          <t>-7,81; 9,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,98; 30,89</t>
+          <t>8,5; 29,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 11,14</t>
+          <t>-1,25; 10,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 10,85</t>
+          <t>-1,2; 11,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,66; 44,82</t>
+          <t>17,15; 45,4</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,96; 111,64</t>
+          <t>-13,95; 125,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,62; 144,59</t>
+          <t>-1,7; 145,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90,4; 487,88</t>
+          <t>94,03; 511,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-20,87; 89,67</t>
+          <t>-21,62; 97,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,71; 61,07</t>
+          <t>-34,77; 66,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,37; 219,27</t>
+          <t>36,37; 208,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 75,86</t>
+          <t>-6,04; 75,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 75,9</t>
+          <t>-6,73; 78,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>86,82; 305,08</t>
+          <t>84,6; 292,06</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 17,03</t>
+          <t>-6,3; 17,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 7,6</t>
+          <t>-12,86; 7,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 25,46</t>
+          <t>2,12; 26,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,08; 27,79</t>
+          <t>5,2; 28,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 6,22</t>
+          <t>-11,66; 6,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,7; 25,79</t>
+          <t>3,6; 25,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,74; 19,2</t>
+          <t>3,16; 19,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 3,91</t>
+          <t>-10,48; 3,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,3; 22,69</t>
+          <t>5,5; 22,75</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-24,09; 151,3</t>
+          <t>-28,24; 155,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-61,66; 74,96</t>
+          <t>-57,57; 72,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 217,62</t>
+          <t>6,91; 221,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21,05; 270,32</t>
+          <t>24,89; 280,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-64,35; 57,91</t>
+          <t>-60,9; 61,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,23; 264,82</t>
+          <t>15,1; 245,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,47; 152,77</t>
+          <t>14,09; 153,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-51,16; 33,02</t>
+          <t>-50,44; 28,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29,87; 188,95</t>
+          <t>25,63; 185,87</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 13,75</t>
+          <t>-7,56; 15,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 20,19</t>
+          <t>-2,97; 21,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,19; 7,41</t>
+          <t>-14,74; 8,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 7,54</t>
+          <t>-13,11; 8,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 22,12</t>
+          <t>-0,82; 21,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-17,73; 5,36</t>
+          <t>-17,26; 5,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 7,52</t>
+          <t>-7,32; 7,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,13; 18,31</t>
+          <t>1,47; 17,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,01; 3,53</t>
+          <t>-13,11; 3,15</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-32,82; 85,76</t>
+          <t>-28,33; 90,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 128,85</t>
+          <t>-12,21; 133,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-57,91; 45,48</t>
+          <t>-55,1; 51,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-50,81; 48,49</t>
+          <t>-50,26; 49,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 140,75</t>
+          <t>-2,5; 148,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-71,38; 33,78</t>
+          <t>-67,33; 40,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-31,64; 44,02</t>
+          <t>-29,57; 43,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,44; 105,87</t>
+          <t>4,92; 102,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-52,49; 20,66</t>
+          <t>-53,96; 19,81</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 26,98</t>
+          <t>-4,32; 27,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-20,24; 7,38</t>
+          <t>-22,13; 5,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,06; 15,63</t>
+          <t>-11,23; 17,65</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 23,83</t>
+          <t>-6,03; 23,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-18,17; 5,73</t>
+          <t>-19,16; 4,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 24,42</t>
+          <t>-5,92; 25,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 21,32</t>
+          <t>-1,34; 20,82</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-16,03; 3,49</t>
+          <t>-15,62; 2,29</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 16,92</t>
+          <t>-4,15; 16,84</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-19,86; 186,47</t>
+          <t>-18,04; 187,91</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-71,14; 53,66</t>
+          <t>-73,17; 52,75</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-43,15; 112,02</t>
+          <t>-40,41; 128,23</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-23,02; 212,1</t>
+          <t>-24,57; 242,14</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-77,43; 60,12</t>
+          <t>-75,33; 47,17</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-29,73; 218,77</t>
+          <t>-29,21; 266,5</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 143,01</t>
+          <t>-5,22; 145,36</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-64,8; 28,62</t>
+          <t>-63,44; 16,93</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-21,94; 119,11</t>
+          <t>-16,87; 126,19</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-14,8; 9,8</t>
+          <t>-15,28; 9,49</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-18,21; 6,3</t>
+          <t>-17,49; 7,36</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-17,58; 5,86</t>
+          <t>-18,67; 6,23</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,73; 25,52</t>
+          <t>-1,03; 24,98</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-13,56; 8,71</t>
+          <t>-14,12; 9,35</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 19,03</t>
+          <t>-5,54; 17,48</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 13,96</t>
+          <t>-3,62; 13,64</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 4,45</t>
+          <t>-12,57; 4,49</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 9,29</t>
+          <t>-8,29; 10,29</t>
         </is>
       </c>
     </row>
@@ -1863,54 +1863,54 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-53,36; 63,99</t>
+          <t>-54,92; 65,64</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-64,2; 41,64</t>
+          <t>-59,66; 56,85</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-63,55; 35,24</t>
+          <t>-63,26; 47,63</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3,25; 211,08</t>
+          <t>-4,32; 188,83</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-58,5; 74,6</t>
+          <t>-63,57; 74,71</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-21,3; 150,77</t>
+          <t>-24,44; 135,61</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-16,8; 88,35</t>
+          <t>-15,26; 87,69</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-51,16; 28,87</t>
+          <t>-52,98; 28,8</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-32,53; 60,2</t>
+          <t>-34,21; 62,69</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 10,99</t>
+          <t>-4,83; 10,56</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-13,64; 0,28</t>
+          <t>-13,35; 0,4</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 15,57</t>
+          <t>-1,33; 15,77</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 5,63</t>
+          <t>-9,82; 5,71</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-18,85; -6,25</t>
+          <t>-18,43; -4,98</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 18,76</t>
+          <t>-0,12; 19,32</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 5,49</t>
+          <t>-4,91; 5,54</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-14,51; -4,72</t>
+          <t>-14,09; -4,69</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,23; 14,75</t>
+          <t>1,76; 14,24</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-25,62; 86,19</t>
+          <t>-24,08; 81,1</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-64,32; 3,49</t>
+          <t>-63,11; 5,61</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 119,6</t>
+          <t>-6,72; 121,39</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-41,79; 34,33</t>
+          <t>-42,11; 38,84</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-79,31; -37,44</t>
+          <t>-78,64; -31,33</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 123,24</t>
+          <t>-1,18; 121,46</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-27,26; 35,82</t>
+          <t>-24,45; 36,44</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-65,54; -27,24</t>
+          <t>-66,67; -29,7</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>10,57; 94,36</t>
+          <t>7,4; 90,04</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 2,33</t>
+          <t>-9,5; 2,46</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 2,36</t>
+          <t>-9,45; 2,4</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-15,96; -4,43</t>
+          <t>-15,49; -4,53</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-18,27; -4,8</t>
+          <t>-18,57; -5,12</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-17,27; -3,21</t>
+          <t>-15,66; -3,18</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-23,53; -10,38</t>
+          <t>-23,77; -10,5</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-12,49; -3,13</t>
+          <t>-12,69; -3,41</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-11,53; -2,1</t>
+          <t>-11,09; -2,53</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-17,57; -9,16</t>
+          <t>-18,09; -9,39</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-48,79; 19,48</t>
+          <t>-47,95; 19,1</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-48,35; 20,82</t>
+          <t>-46,75; 21,09</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-81,22; -31,84</t>
+          <t>-80,63; -32,87</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-65,54; -22,37</t>
+          <t>-65,66; -23,27</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-58,9; -13,4</t>
+          <t>-57,11; -13,39</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-83,34; -47,8</t>
+          <t>-82,14; -47,08</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-53,92; -17,04</t>
+          <t>-55,13; -18,51</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-49,63; -11,73</t>
+          <t>-48,43; -13,69</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-77,2; -49,84</t>
+          <t>-77,93; -51,64</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 6,0</t>
+          <t>-1,19; 5,73</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 2,73</t>
+          <t>-3,52; 2,82</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3,55; 18,68</t>
+          <t>3,37; 19,5</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 4,37</t>
+          <t>-2,47; 4,39</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-6,64; -0,23</t>
+          <t>-6,91; -0,09</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 7,6</t>
+          <t>0,53; 7,5</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 4,24</t>
+          <t>-0,96; 4,02</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 0,37</t>
+          <t>-4,44; 0,25</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>3,2; 11,67</t>
+          <t>3,11; 11,58</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 35,93</t>
+          <t>-6,23; 33,43</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-19,16; 16,14</t>
+          <t>-18,08; 16,95</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>17,95; 107,36</t>
+          <t>17,42; 112,51</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 23,94</t>
+          <t>-11,14; 24,47</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-30,26; -1,01</t>
+          <t>-31,19; -0,16</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 41,43</t>
+          <t>2,39; 41,04</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 23,55</t>
+          <t>-4,67; 22,57</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-21,61; 2,04</t>
+          <t>-21,34; 1,47</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>15,68; 61,83</t>
+          <t>15,21; 62,4</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP15-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP15-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 17,71</t>
+          <t>-7,24; 19,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 18,17</t>
+          <t>-8,98; 18,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,11; 36,17</t>
+          <t>4,58; 36,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 20,55</t>
+          <t>-4,47; 21,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 21,76</t>
+          <t>-4,92; 21,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 20,63</t>
+          <t>-5,28; 19,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 16,65</t>
+          <t>-1,22; 16,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 17,36</t>
+          <t>-1,19; 17,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,93; 24,47</t>
+          <t>3,78; 24,57</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-28,47; 113,82</t>
+          <t>-25,25; 121,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-28,0; 117,73</t>
+          <t>-31,06; 118,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,89; 221,64</t>
+          <t>15,44; 235,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,21; 137,1</t>
+          <t>-18,14; 156,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 150,48</t>
+          <t>-17,74; 154,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,73; 144,34</t>
+          <t>-20,36; 135,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 98,26</t>
+          <t>-5,12; 101,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 106,12</t>
+          <t>-5,24; 99,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,34; 147,23</t>
+          <t>14,14; 136,21</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 15,18</t>
+          <t>-2,16; 15,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 17,98</t>
+          <t>-0,24; 18,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,37; 59,33</t>
+          <t>17,21; 59,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 13,05</t>
+          <t>-4,34; 12,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 9,16</t>
+          <t>-6,55; 9,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,5; 29,98</t>
+          <t>8,82; 29,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 10,76</t>
+          <t>-1,16; 10,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 11,25</t>
+          <t>-0,56; 11,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,15; 45,4</t>
+          <t>17,48; 45,99</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,95; 125,26</t>
+          <t>-10,53; 134,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 145,85</t>
+          <t>-0,74; 147,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94,03; 511,41</t>
+          <t>94,25; 521,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,62; 97,59</t>
+          <t>-21,11; 91,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,77; 66,9</t>
+          <t>-31,24; 64,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,37; 208,04</t>
+          <t>43,22; 212,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 75,99</t>
+          <t>-5,62; 77,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 78,29</t>
+          <t>-1,89; 77,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>84,6; 292,06</t>
+          <t>86,72; 287,0</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 17,21</t>
+          <t>-5,97; 16,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 7,84</t>
+          <t>-12,58; 7,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,12; 26,65</t>
+          <t>1,39; 25,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,2; 28,48</t>
+          <t>5,86; 28,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 6,32</t>
+          <t>-12,0; 6,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,6; 25,56</t>
+          <t>3,62; 26,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,16; 19,0</t>
+          <t>2,55; 18,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,48; 3,64</t>
+          <t>-10,73; 3,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,5; 22,75</t>
+          <t>5,81; 22,85</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-28,24; 155,09</t>
+          <t>-28,81; 143,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-57,57; 72,16</t>
+          <t>-57,32; 70,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,91; 221,26</t>
+          <t>4,43; 213,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24,89; 280,47</t>
+          <t>29,56; 301,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-60,9; 61,23</t>
+          <t>-61,13; 57,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,1; 245,98</t>
+          <t>15,61; 261,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,09; 153,01</t>
+          <t>10,38; 150,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,44; 28,49</t>
+          <t>-51,86; 29,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25,63; 185,87</t>
+          <t>26,39; 181,24</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 15,15</t>
+          <t>-8,04; 14,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 21,32</t>
+          <t>-2,16; 21,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,74; 8,51</t>
+          <t>-15,82; 7,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,11; 8,13</t>
+          <t>-12,47; 8,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 21,67</t>
+          <t>-1,47; 22,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-17,26; 5,51</t>
+          <t>-17,74; 5,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 7,38</t>
+          <t>-7,19; 8,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 17,94</t>
+          <t>1,42; 17,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,11; 3,15</t>
+          <t>-13,42; 2,64</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,33; 90,82</t>
+          <t>-30,84; 88,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,21; 133,32</t>
+          <t>-10,05; 135,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-55,1; 51,79</t>
+          <t>-58,36; 43,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-50,26; 49,97</t>
+          <t>-48,58; 56,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 148,22</t>
+          <t>-5,86; 146,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-67,33; 40,78</t>
+          <t>-69,49; 36,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,57; 43,71</t>
+          <t>-29,59; 46,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,92; 102,03</t>
+          <t>5,65; 108,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-53,96; 19,81</t>
+          <t>-54,44; 13,87</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 27,57</t>
+          <t>-5,11; 26,89</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-22,13; 5,48</t>
+          <t>-20,7; 7,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 17,65</t>
+          <t>-12,26; 17,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 23,38</t>
+          <t>-4,17; 22,47</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-19,16; 4,46</t>
+          <t>-17,67; 5,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 25,48</t>
+          <t>-6,38; 24,19</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 20,82</t>
+          <t>-1,12; 21,62</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-15,62; 2,29</t>
+          <t>-16,16; 3,24</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 16,84</t>
+          <t>-4,66; 16,82</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-18,04; 187,91</t>
+          <t>-23,6; 187,27</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-73,17; 52,75</t>
+          <t>-71,9; 66,69</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-40,41; 128,23</t>
+          <t>-41,71; 119,85</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,57; 242,14</t>
+          <t>-19,67; 210,09</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-75,33; 47,17</t>
+          <t>-74,87; 53,55</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-29,21; 266,5</t>
+          <t>-27,12; 238,91</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 145,36</t>
+          <t>-7,05; 150,45</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-63,44; 16,93</t>
+          <t>-65,73; 22,27</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-16,87; 126,19</t>
+          <t>-21,04; 112,34</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-15,28; 9,49</t>
+          <t>-14,26; 9,93</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-17,49; 7,36</t>
+          <t>-17,01; 7,27</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-18,67; 6,23</t>
+          <t>-17,63; 6,81</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 24,98</t>
+          <t>-0,91; 24,07</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-14,12; 9,35</t>
+          <t>-14,19; 8,87</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 17,48</t>
+          <t>-4,98; 18,56</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 13,64</t>
+          <t>-2,65; 14,27</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-12,57; 4,49</t>
+          <t>-11,67; 4,75</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 10,29</t>
+          <t>-6,89; 9,96</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-54,92; 65,64</t>
+          <t>-52,09; 60,73</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-59,66; 56,85</t>
+          <t>-59,49; 50,9</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-63,26; 47,63</t>
+          <t>-63,14; 46,79</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 188,83</t>
+          <t>-5,26; 190,57</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-63,57; 74,71</t>
+          <t>-61,37; 74,42</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-24,44; 135,61</t>
+          <t>-21,64; 151,84</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-15,26; 87,69</t>
+          <t>-11,96; 92,63</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-52,98; 28,8</t>
+          <t>-48,72; 33,17</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-34,21; 62,69</t>
+          <t>-29,88; 60,65</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 10,56</t>
+          <t>-5,3; 9,83</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 0,4</t>
+          <t>-13,27; 0,07</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 15,77</t>
+          <t>-1,43; 15,86</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 5,71</t>
+          <t>-10,16; 5,68</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-18,43; -4,98</t>
+          <t>-18,93; -5,71</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 19,32</t>
+          <t>-0,25; 19,65</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 5,54</t>
+          <t>-5,2; 5,43</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-14,09; -4,69</t>
+          <t>-14,23; -4,12</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,76; 14,24</t>
+          <t>1,98; 15,17</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-24,08; 81,1</t>
+          <t>-25,63; 73,38</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-63,11; 5,61</t>
+          <t>-62,85; 3,08</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 121,39</t>
+          <t>-7,32; 121,08</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-42,11; 38,84</t>
+          <t>-43,08; 37,07</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-78,64; -31,33</t>
+          <t>-79,31; -36,66</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 121,46</t>
+          <t>-1,23; 125,65</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-24,45; 36,44</t>
+          <t>-24,98; 36,53</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-66,67; -29,7</t>
+          <t>-66,93; -28,16</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>7,4; 90,04</t>
+          <t>8,12; 98,5</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 2,46</t>
+          <t>-9,8; 2,97</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 2,4</t>
+          <t>-9,6; 2,18</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-15,49; -4,53</t>
+          <t>-15,74; -4,24</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-18,57; -5,12</t>
+          <t>-18,23; -4,91</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-15,66; -3,18</t>
+          <t>-15,81; -2,66</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-23,77; -10,5</t>
+          <t>-23,59; -10,61</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-12,69; -3,41</t>
+          <t>-12,05; -2,94</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-11,09; -2,53</t>
+          <t>-11,02; -1,88</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-18,09; -9,39</t>
+          <t>-17,66; -8,95</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-47,95; 19,1</t>
+          <t>-49,93; 23,56</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-46,75; 21,09</t>
+          <t>-48,31; 16,55</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-80,63; -32,87</t>
+          <t>-79,28; -30,16</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-65,66; -23,27</t>
+          <t>-65,18; -23,89</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-57,11; -13,39</t>
+          <t>-57,12; -12,69</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-82,14; -47,08</t>
+          <t>-83,27; -49,75</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-55,13; -18,51</t>
+          <t>-52,9; -16,29</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-48,43; -13,69</t>
+          <t>-47,98; -10,62</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-77,93; -51,64</t>
+          <t>-76,95; -49,19</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 5,73</t>
+          <t>-1,29; 5,9</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 2,82</t>
+          <t>-3,86; 2,64</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3,37; 19,5</t>
+          <t>3,24; 18,79</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 4,39</t>
+          <t>-2,18; 4,61</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-6,91; -0,09</t>
+          <t>-6,66; -0,1</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,53; 7,5</t>
+          <t>0,37; 8,13</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 4,02</t>
+          <t>-0,58; 4,15</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 0,25</t>
+          <t>-4,04; 0,4</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>3,11; 11,58</t>
+          <t>3,17; 10,59</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 33,43</t>
+          <t>-6,72; 34,41</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 16,95</t>
+          <t>-19,63; 15,96</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>17,42; 112,51</t>
+          <t>16,31; 104,05</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 24,47</t>
+          <t>-10,22; 25,21</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-31,19; -0,16</t>
+          <t>-30,25; -0,48</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2,39; 41,04</t>
+          <t>1,65; 44,81</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 22,57</t>
+          <t>-2,82; 23,35</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-21,34; 1,47</t>
+          <t>-19,67; 2,2</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>15,21; 62,4</t>
+          <t>15,42; 56,87</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP15-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP15-Provincia-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..)</t>
+          <t>Menores que consumieron algún tipo de medicamento en las últimas 2 semanas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8,6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9,64</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9,89</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>5,83</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>5,85</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19,27</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8,6</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9,64</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,97</t>
+          <t>14,63</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13,42</t>
+          <t>12,12</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 19,41</t>
+          <t>-6,98; 20,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 18,95</t>
+          <t>-3,01; 23,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,58; 36,02</t>
+          <t>-3,77; 22,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 21,79</t>
+          <t>-8,79; 18,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 21,19</t>
+          <t>-8,13; 19,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 19,98</t>
+          <t>1,37; 27,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 16,81</t>
+          <t>-1,49; 16,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 17,11</t>
+          <t>-1,54; 16,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,78; 24,57</t>
+          <t>2,99; 21,18</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>42,65%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>47,84%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>49,09%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>26,24%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>26,37%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>86,8%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>42,65%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>47,84%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>57,41%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-25,25; 121,32</t>
+          <t>-27,55; 141,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-31,06; 118,86</t>
+          <t>-13,39; 174,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,44; 235,62</t>
+          <t>-14,92; 170,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,14; 156,77</t>
+          <t>-31,24; 108,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-17,74; 154,46</t>
+          <t>-29,21; 121,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,36; 135,11</t>
+          <t>4,93; 180,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 101,8</t>
+          <t>-6,6; 98,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 99,48</t>
+          <t>-5,18; 99,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,14; 136,21</t>
+          <t>11,05; 124,68</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,21</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18,58</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>5,95</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>9,76</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>34,65</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,21</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,5</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,49</t>
+          <t>22,42</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>26,93</t>
+          <t>20,39</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 15,63</t>
+          <t>-4,54; 12,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 18,16</t>
+          <t>-7,78; 8,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,21; 59,23</t>
+          <t>7,81; 29,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 12,6</t>
+          <t>-3,55; 13,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 9,27</t>
+          <t>1,03; 18,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,82; 29,56</t>
+          <t>11,07; 32,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 10,99</t>
+          <t>-1,65; 11,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 11,07</t>
+          <t>-1,07; 10,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,48; 45,99</t>
+          <t>12,86; 27,65</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>23,07%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>101,76%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>36,14%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>59,22%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>210,35%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>23,07%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>106,75%</t>
+          <t>136,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>154,79%</t>
+          <t>117,22%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,53; 134,52</t>
+          <t>-20,87; 89,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 147,03</t>
+          <t>-34,71; 61,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94,25; 521,21</t>
+          <t>34,8; 212,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,11; 91,62</t>
+          <t>-17,96; 111,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,24; 64,79</t>
+          <t>4,62; 144,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,22; 212,69</t>
+          <t>51,36; 256,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 77,42</t>
+          <t>-8,84; 75,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 77,17</t>
+          <t>-5,85; 75,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>86,72; 287,0</t>
+          <t>63,53; 194,73</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>16,29</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-3,09</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>14,76</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>5,58</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-2,95</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>13,59</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>16,29</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-3,09</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,19</t>
+          <t>13,21</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14,39</t>
+          <t>14,0</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 16,62</t>
+          <t>5,08; 27,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 7,45</t>
+          <t>-12,4; 6,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,39; 25,63</t>
+          <t>3,28; 25,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,86; 28,36</t>
+          <t>-4,81; 17,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 6,19</t>
+          <t>-13,61; 7,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,62; 26,1</t>
+          <t>0,8; 25,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,55; 18,84</t>
+          <t>2,74; 19,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 3,65</t>
+          <t>-9,95; 3,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,81; 22,85</t>
+          <t>6,12; 22,23</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>108,49%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-20,56%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>98,27%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>32,43%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-17,16%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>79,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>108,49%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-20,56%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>101,14%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>87,0%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-28,81; 143,02</t>
+          <t>21,05; 270,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-57,32; 70,97</t>
+          <t>-64,35; 57,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,43; 213,33</t>
+          <t>15,33; 262,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29,56; 301,72</t>
+          <t>-24,09; 151,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-61,13; 57,8</t>
+          <t>-61,66; 74,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,61; 261,37</t>
+          <t>-0,45; 216,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,38; 150,29</t>
+          <t>12,47; 152,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-51,86; 29,09</t>
+          <t>-51,16; 33,02</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26,39; 181,24</t>
+          <t>29,28; 186,78</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-2,23</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10,75</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-6,33</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>3,0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>9,08</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-3,99</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-2,23</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>10,75</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-6,59</t>
+          <t>-4,59</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-5,38</t>
+          <t>-5,46</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 14,98</t>
+          <t>-13,54; 7,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 21,81</t>
+          <t>-0,97; 22,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,82; 7,28</t>
+          <t>-17,57; 6,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,47; 8,21</t>
+          <t>-8,62; 13,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 22,22</t>
+          <t>-3,78; 20,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-17,74; 5,37</t>
+          <t>-15,95; 7,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 8,21</t>
+          <t>-8,35; 7,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,42; 17,62</t>
+          <t>2,13; 18,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 2,64</t>
+          <t>-12,93; 3,78</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-10,73%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>51,75%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-30,48%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>13,74%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>41,57%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-18,28%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-10,73%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>51,75%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-31,75%</t>
+          <t>-21,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-25,26%</t>
+          <t>-25,64%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-30,84; 88,4</t>
+          <t>-50,81; 48,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 135,53</t>
+          <t>-5,39; 140,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-58,36; 43,37</t>
+          <t>-70,73; 39,2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-48,58; 56,32</t>
+          <t>-32,82; 85,76</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 146,72</t>
+          <t>-14,18; 128,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-69,49; 36,89</t>
+          <t>-58,29; 42,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,59; 46,89</t>
+          <t>-31,64; 44,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,65; 108,09</t>
+          <t>7,44; 105,87</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-54,44; 13,87</t>
+          <t>-52,34; 20,73</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>8,84</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-6,29</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>7,17</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>11,24</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-6,82</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2,06</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>8,84</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-6,29</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,81</t>
+          <t>1,9</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5,61</t>
+          <t>4,63</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 26,89</t>
+          <t>-4,7; 23,83</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-20,7; 7,16</t>
+          <t>-18,17; 5,73</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 17,11</t>
+          <t>-6,46; 22,9</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 22,47</t>
+          <t>-5,76; 26,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 5,19</t>
+          <t>-20,24; 7,38</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 24,19</t>
+          <t>-12,15; 15,75</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 21,62</t>
+          <t>-0,35; 21,32</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-16,16; 3,24</t>
+          <t>-16,03; 3,49</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 16,82</t>
+          <t>-5,58; 15,87</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>50,71%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-36,07%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>41,12%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>51,54%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-31,27%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>9,45%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>50,71%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-36,07%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>23,7%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-23,6; 187,27</t>
+          <t>-23,02; 212,1</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-71,9; 66,69</t>
+          <t>-77,43; 60,12</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-41,71; 119,85</t>
+          <t>-33,64; 202,01</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-19,67; 210,09</t>
+          <t>-19,86; 186,47</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-74,87; 53,55</t>
+          <t>-71,14; 53,66</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-27,12; 238,91</t>
+          <t>-43,71; 110,49</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 150,45</t>
+          <t>-1,92; 143,01</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-65,73; 22,27</t>
+          <t>-64,8; 28,62</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-21,04; 112,34</t>
+          <t>-23,5; 113,95</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>12,07</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-2,92</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>5,41</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-2,46</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-5,31</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-5,45</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>12,07</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-2,92</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,26</t>
+          <t>-5,34</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,21</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 9,93</t>
+          <t>0,73; 25,52</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-17,01; 7,27</t>
+          <t>-13,56; 8,71</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-17,63; 6,81</t>
+          <t>-5,26; 18,06</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 24,07</t>
+          <t>-14,8; 9,8</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-14,19; 8,87</t>
+          <t>-18,21; 6,3</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 18,56</t>
+          <t>-17,84; 5,88</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 14,27</t>
+          <t>-3,94; 13,96</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 4,75</t>
+          <t>-12,31; 4,45</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 9,96</t>
+          <t>-7,91; 8,76</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>67,2%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-16,25%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>30,11%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-11,13%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-24,04%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-24,68%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>67,2%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-16,25%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>-24,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-52,09; 60,73</t>
+          <t>3,25; 211,08</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-59,49; 50,9</t>
+          <t>-58,5; 74,6</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-63,14; 46,79</t>
+          <t>-24,51; 144,77</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 190,57</t>
+          <t>-53,36; 63,99</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-61,37; 74,42</t>
+          <t>-64,2; 41,64</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-21,64; 151,84</t>
+          <t>-63,12; 40,66</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 92,63</t>
+          <t>-16,8; 88,35</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-48,72; 33,17</t>
+          <t>-51,16; 28,87</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-29,88; 60,65</t>
+          <t>-34,34; 59,62</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-2,16</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-12,19</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>10,18</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>2,43</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-6,34</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>7,21</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-2,16</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-12,19</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,88</t>
+          <t>7,99</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>8,26</t>
+          <t>9,22</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 9,83</t>
+          <t>-9,85; 5,63</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 0,07</t>
+          <t>-18,85; -6,25</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 15,86</t>
+          <t>0,89; 20,5</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 5,68</t>
+          <t>-5,24; 10,99</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-18,93; -5,71</t>
+          <t>-13,64; 0,28</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 19,65</t>
+          <t>-0,03; 16,46</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 5,43</t>
+          <t>-5,57; 5,49</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-14,23; -4,12</t>
+          <t>-14,51; -4,72</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,98; 15,17</t>
+          <t>3,17; 15,69</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-11,06%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-62,36%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>52,06%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>14,54%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-37,94%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>43,12%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-11,06%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-62,36%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>50,76%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-25,63; 73,38</t>
+          <t>-41,79; 34,33</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-62,85; 3,08</t>
+          <t>-79,31; -37,44</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 121,08</t>
+          <t>3,49; 133,79</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-43,08; 37,07</t>
+          <t>-25,62; 86,19</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-79,31; -36,66</t>
+          <t>-64,32; 3,49</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 125,65</t>
+          <t>-1,48; 128,3</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-24,98; 36,53</t>
+          <t>-27,26; 35,82</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-66,93; -28,16</t>
+          <t>-65,54; -27,24</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>8,12; 98,5</t>
+          <t>14,98; 99,89</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-11,53</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-9,66</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-16,93</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-3,53</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>-3,68</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-10,25</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-11,53</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-9,66</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-16,8</t>
+          <t>-10,98</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-13,55</t>
+          <t>-13,97</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 2,97</t>
+          <t>-18,27; -4,8</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 2,18</t>
+          <t>-17,27; -3,21</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-15,74; -4,24</t>
+          <t>-23,65; -10,37</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-18,23; -4,91</t>
+          <t>-9,37; 2,33</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-15,81; -2,66</t>
+          <t>-9,59; 2,36</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-23,59; -10,61</t>
+          <t>-16,59; -5,25</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-12,05; -2,94</t>
+          <t>-12,49; -3,13</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-11,02; -1,88</t>
+          <t>-11,53; -2,1</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-17,66; -8,95</t>
+          <t>-17,96; -9,69</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-47,43%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-39,75%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-69,66%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-21,52%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>-22,39%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-62,46%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-47,43%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-39,75%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-69,14%</t>
+          <t>-66,9%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-66,29%</t>
+          <t>-68,38%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-49,93; 23,56</t>
+          <t>-65,54; -22,37</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-48,31; 16,55</t>
+          <t>-58,9; -13,4</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-79,28; -30,16</t>
+          <t>-83,5; -47,55</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-65,18; -23,89</t>
+          <t>-48,79; 19,48</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-57,12; -12,69</t>
+          <t>-48,35; 20,82</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-83,27; -49,75</t>
+          <t>-84,02; -38,85</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-52,9; -16,29</t>
+          <t>-53,92; -17,04</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-47,98; -10,62</t>
+          <t>-49,63; -11,73</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-76,95; -49,19</t>
+          <t>-78,85; -52,51</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>1,17</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-3,36</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>3,64</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>2,36</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>-0,3</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>8,45</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>1,17</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-3,36</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,02</t>
+          <t>4,37</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>6,11</t>
+          <t>4,01</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 5,9</t>
+          <t>-2,38; 4,37</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 2,64</t>
+          <t>-6,64; -0,23</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3,24; 18,79</t>
+          <t>-0,82; 7,28</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 4,61</t>
+          <t>-0,75; 6,0</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-6,66; -0,1</t>
+          <t>-3,84; 2,73</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,37; 8,13</t>
+          <t>0,88; 8,48</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 4,15</t>
+          <t>-0,93; 4,24</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 0,4</t>
+          <t>-4,4; 0,37</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>3,17; 10,59</t>
+          <t>1,44; 6,84</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-16,89%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>18,3%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>12,84%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>-1,65%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>45,94%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>5,89%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-16,89%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 34,41</t>
+          <t>-10,96; 23,94</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-19,63; 15,96</t>
+          <t>-30,26; -1,01</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>16,31; 104,05</t>
+          <t>-3,76; 38,84</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-10,22; 25,21</t>
+          <t>-3,71; 35,93</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-30,25; -0,48</t>
+          <t>-19,16; 16,14</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1,65; 44,81</t>
+          <t>4,36; 49,64</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 23,35</t>
+          <t>-4,57; 23,55</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-19,67; 2,2</t>
+          <t>-21,61; 2,04</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>15,42; 56,87</t>
+          <t>7,06; 38,42</t>
         </is>
       </c>
     </row>
